--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,3172 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123049756</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90940</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>597344</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7030297</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123039792</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91235</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>658</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>597458</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7030292</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123042937</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>597397</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7030367</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123042345</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>597413</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7030346</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123042680</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91235</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>658</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>597383</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7030347</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123050244</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90940</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>597436</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7030329</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123041379</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91235</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>658</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>597386</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7030293</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123041901</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90940</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>597380</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7030371</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123041570</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>597395</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7030312</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123040568</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91389</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>597441</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7030301</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123044289</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79876</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>597317</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7030322</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123044251</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>597321</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7030312</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123043324</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>597342</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7030326</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123043079</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90909</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>597393</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7030365</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123045077</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90909</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>597313</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7030320</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123051419</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90940</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>597335</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7030341</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123041516</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91389</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>597391</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7030295</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123040577</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>597442</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7030306</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123040637</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91342</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>597437</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7030292</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123044298</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>597315</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7030325</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123041496</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>597392</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7030296</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123041955</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>597379</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7030360</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123044316</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79882</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>597313</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7030320</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123041564</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91389</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>597391</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7030308</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123052262</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>597377</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7030279</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123052146</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>597309</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7030317</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123039951</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>597462</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7030312</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123052224</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90940</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>597309</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7030317</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123044293</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>597316</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7030324</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123041531</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90940</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>597390</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7030296</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123039722</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>597461</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7030329</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123041379</v>
+        <v>123041901</v>
       </c>
       <c r="B9" t="n">
-        <v>91235</v>
+        <v>90940</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597386</v>
+        <v>597380</v>
       </c>
       <c r="R9" t="n">
-        <v>7030293</v>
+        <v>7030371</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123041901</v>
+        <v>123041379</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>91235</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597380</v>
+        <v>597386</v>
       </c>
       <c r="R10" t="n">
-        <v>7030371</v>
+        <v>7030293</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123041570</v>
+        <v>123040568</v>
       </c>
       <c r="B11" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,25 +1619,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597395</v>
+        <v>597441</v>
       </c>
       <c r="R11" t="n">
-        <v>7030312</v>
+        <v>7030301</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123040568</v>
+        <v>123041570</v>
       </c>
       <c r="B12" t="n">
-        <v>91389</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,25 +1721,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597441</v>
+        <v>597395</v>
       </c>
       <c r="R12" t="n">
-        <v>7030301</v>
+        <v>7030312</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123045077</v>
+        <v>123051419</v>
       </c>
       <c r="B17" t="n">
-        <v>90909</v>
+        <v>90940</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597313</v>
+        <v>597335</v>
       </c>
       <c r="R17" t="n">
-        <v>7030320</v>
+        <v>7030341</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123051419</v>
+        <v>123045077</v>
       </c>
       <c r="B18" t="n">
-        <v>90940</v>
+        <v>90909</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,25 +2333,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597335</v>
+        <v>597313</v>
       </c>
       <c r="R18" t="n">
-        <v>7030341</v>
+        <v>7030320</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123041496</v>
+        <v>123044316</v>
       </c>
       <c r="B23" t="n">
-        <v>90944</v>
+        <v>79882</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,25 +2838,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597392</v>
+        <v>597313</v>
       </c>
       <c r="R23" t="n">
-        <v>7030296</v>
+        <v>7030320</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123041955</v>
+        <v>123041496</v>
       </c>
       <c r="B24" t="n">
         <v>90944</v>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597379</v>
+        <v>597392</v>
       </c>
       <c r="R24" t="n">
-        <v>7030360</v>
+        <v>7030296</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123044316</v>
+        <v>123041955</v>
       </c>
       <c r="B25" t="n">
-        <v>79882</v>
+        <v>90944</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597313</v>
+        <v>597379</v>
       </c>
       <c r="R25" t="n">
-        <v>7030320</v>
+        <v>7030360</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3955,6 +3955,112 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123071993</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91605</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>898</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>597336</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7030304</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -1607,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123040568</v>
+        <v>123041570</v>
       </c>
       <c r="B11" t="n">
-        <v>91389</v>
+        <v>90944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,25 +1619,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597441</v>
+        <v>597395</v>
       </c>
       <c r="R11" t="n">
-        <v>7030301</v>
+        <v>7030312</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123041570</v>
+        <v>123040568</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,25 +1721,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597395</v>
+        <v>597441</v>
       </c>
       <c r="R12" t="n">
-        <v>7030312</v>
+        <v>7030301</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123044316</v>
+        <v>123041496</v>
       </c>
       <c r="B23" t="n">
-        <v>79882</v>
+        <v>90944</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,25 +2838,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597313</v>
+        <v>597392</v>
       </c>
       <c r="R23" t="n">
-        <v>7030320</v>
+        <v>7030296</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2928,7 +2928,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123041496</v>
+        <v>123041955</v>
       </c>
       <c r="B24" t="n">
         <v>90944</v>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597392</v>
+        <v>597379</v>
       </c>
       <c r="R24" t="n">
-        <v>7030296</v>
+        <v>7030360</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3030,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123041955</v>
+        <v>123044316</v>
       </c>
       <c r="B25" t="n">
-        <v>90944</v>
+        <v>79882</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597379</v>
+        <v>597313</v>
       </c>
       <c r="R25" t="n">
-        <v>7030360</v>
+        <v>7030320</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123044293</v>
+        <v>123041531</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>90940</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597316</v>
+        <v>597390</v>
       </c>
       <c r="R31" t="n">
-        <v>7030324</v>
+        <v>7030296</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123041531</v>
+        <v>123039722</v>
       </c>
       <c r="B32" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3769,21 +3769,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597390</v>
+        <v>597461</v>
       </c>
       <c r="R32" t="n">
-        <v>7030296</v>
+        <v>7030329</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123039722</v>
+        <v>123044293</v>
       </c>
       <c r="B33" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3871,21 +3871,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597461</v>
+        <v>597316</v>
       </c>
       <c r="R33" t="n">
-        <v>7030329</v>
+        <v>7030324</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123049756</v>
+        <v>123045077</v>
       </c>
       <c r="B3" t="n">
-        <v>90940</v>
+        <v>90917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597344</v>
+        <v>597313</v>
       </c>
       <c r="R3" t="n">
-        <v>7030297</v>
+        <v>7030320</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123039792</v>
+        <v>123042680</v>
       </c>
       <c r="B4" t="n">
-        <v>91235</v>
+        <v>91243</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597458</v>
+        <v>597383</v>
       </c>
       <c r="R4" t="n">
-        <v>7030292</v>
+        <v>7030347</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123042937</v>
+        <v>123042345</v>
       </c>
       <c r="B5" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597397</v>
+        <v>597413</v>
       </c>
       <c r="R5" t="n">
-        <v>7030367</v>
+        <v>7030346</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123042345</v>
+        <v>123041955</v>
       </c>
       <c r="B6" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597413</v>
+        <v>597379</v>
       </c>
       <c r="R6" t="n">
-        <v>7030346</v>
+        <v>7030360</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123042680</v>
+        <v>123044251</v>
       </c>
       <c r="B7" t="n">
-        <v>91235</v>
+        <v>90952</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597383</v>
+        <v>597321</v>
       </c>
       <c r="R7" t="n">
-        <v>7030347</v>
+        <v>7030312</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123050244</v>
+        <v>123052224</v>
       </c>
       <c r="B8" t="n">
-        <v>90940</v>
+        <v>90948</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597436</v>
+        <v>597309</v>
       </c>
       <c r="R8" t="n">
-        <v>7030329</v>
+        <v>7030317</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123041901</v>
+        <v>123039951</v>
       </c>
       <c r="B9" t="n">
-        <v>90940</v>
+        <v>90952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597380</v>
+        <v>597462</v>
       </c>
       <c r="R9" t="n">
-        <v>7030371</v>
+        <v>7030312</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123041379</v>
+        <v>123050244</v>
       </c>
       <c r="B10" t="n">
-        <v>91235</v>
+        <v>90948</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597386</v>
+        <v>597436</v>
       </c>
       <c r="R10" t="n">
-        <v>7030293</v>
+        <v>7030329</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1607,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123041570</v>
+        <v>123043079</v>
       </c>
       <c r="B11" t="n">
-        <v>90944</v>
+        <v>90917</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,25 +1619,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597395</v>
+        <v>597393</v>
       </c>
       <c r="R11" t="n">
-        <v>7030312</v>
+        <v>7030365</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123040568</v>
+        <v>123052146</v>
       </c>
       <c r="B12" t="n">
-        <v>91389</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,38 +1721,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597441</v>
+        <v>597309</v>
       </c>
       <c r="R12" t="n">
-        <v>7030301</v>
+        <v>7030317</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1811,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123044289</v>
+        <v>123052262</v>
       </c>
       <c r="B13" t="n">
-        <v>79876</v>
+        <v>90952</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,25 +1832,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597317</v>
+        <v>597377</v>
       </c>
       <c r="R13" t="n">
-        <v>7030322</v>
+        <v>7030279</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1913,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123044251</v>
+        <v>123044316</v>
       </c>
       <c r="B14" t="n">
-        <v>90944</v>
+        <v>79882</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,25 +1934,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1953,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597321</v>
+        <v>597313</v>
       </c>
       <c r="R14" t="n">
-        <v>7030312</v>
+        <v>7030320</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2015,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123043324</v>
+        <v>123044293</v>
       </c>
       <c r="B15" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2031,21 +2040,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597342</v>
+        <v>597316</v>
       </c>
       <c r="R15" t="n">
-        <v>7030326</v>
+        <v>7030324</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2117,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123043079</v>
+        <v>123041516</v>
       </c>
       <c r="B16" t="n">
-        <v>90909</v>
+        <v>91397</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,25 +2138,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597393</v>
+        <v>597391</v>
       </c>
       <c r="R16" t="n">
-        <v>7030365</v>
+        <v>7030295</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2219,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123051419</v>
+        <v>123041379</v>
       </c>
       <c r="B17" t="n">
-        <v>90940</v>
+        <v>91243</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2244,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597335</v>
+        <v>597386</v>
       </c>
       <c r="R17" t="n">
-        <v>7030341</v>
+        <v>7030293</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2321,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123045077</v>
+        <v>123040637</v>
       </c>
       <c r="B18" t="n">
-        <v>90909</v>
+        <v>91350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,25 +2342,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597313</v>
+        <v>597437</v>
       </c>
       <c r="R18" t="n">
-        <v>7030320</v>
+        <v>7030292</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2423,10 +2427,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123041516</v>
+        <v>123041901</v>
       </c>
       <c r="B19" t="n">
-        <v>91389</v>
+        <v>90948</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2435,25 +2439,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597391</v>
+        <v>597380</v>
       </c>
       <c r="R19" t="n">
-        <v>7030295</v>
+        <v>7030371</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2525,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123040577</v>
+        <v>123044298</v>
       </c>
       <c r="B20" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2541,21 +2545,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597442</v>
+        <v>597315</v>
       </c>
       <c r="R20" t="n">
-        <v>7030306</v>
+        <v>7030325</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2627,10 +2631,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123040637</v>
+        <v>123041496</v>
       </c>
       <c r="B21" t="n">
-        <v>91342</v>
+        <v>90952</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2643,16 +2647,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597437</v>
+        <v>597392</v>
       </c>
       <c r="R21" t="n">
-        <v>7030292</v>
+        <v>7030296</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2724,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123044298</v>
+        <v>123042937</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2749,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2773,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597315</v>
+        <v>597397</v>
       </c>
       <c r="R22" t="n">
-        <v>7030325</v>
+        <v>7030367</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2826,10 +2835,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123041496</v>
+        <v>123051419</v>
       </c>
       <c r="B23" t="n">
-        <v>90944</v>
+        <v>90948</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2851,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597392</v>
+        <v>597335</v>
       </c>
       <c r="R23" t="n">
-        <v>7030296</v>
+        <v>7030341</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2928,10 +2937,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123041955</v>
+        <v>123043324</v>
       </c>
       <c r="B24" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2968,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597379</v>
+        <v>597342</v>
       </c>
       <c r="R24" t="n">
-        <v>7030360</v>
+        <v>7030326</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3030,10 +3039,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123044316</v>
+        <v>123039792</v>
       </c>
       <c r="B25" t="n">
-        <v>79882</v>
+        <v>91243</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3051,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597313</v>
+        <v>597458</v>
       </c>
       <c r="R25" t="n">
-        <v>7030320</v>
+        <v>7030292</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3132,10 +3141,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123041564</v>
+        <v>123041570</v>
       </c>
       <c r="B26" t="n">
-        <v>91389</v>
+        <v>90952</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,25 +3153,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597391</v>
+        <v>597395</v>
       </c>
       <c r="R26" t="n">
-        <v>7030308</v>
+        <v>7030312</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3234,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123052262</v>
+        <v>123040568</v>
       </c>
       <c r="B27" t="n">
-        <v>90944</v>
+        <v>91397</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,25 +3255,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597377</v>
+        <v>597441</v>
       </c>
       <c r="R27" t="n">
-        <v>7030279</v>
+        <v>7030301</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3336,10 +3345,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123052146</v>
+        <v>123049756</v>
       </c>
       <c r="B28" t="n">
-        <v>57631</v>
+        <v>90948</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,43 +3361,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597309</v>
+        <v>597344</v>
       </c>
       <c r="R28" t="n">
-        <v>7030317</v>
+        <v>7030297</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123039951</v>
+        <v>123039722</v>
       </c>
       <c r="B29" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597462</v>
+        <v>597461</v>
       </c>
       <c r="R29" t="n">
-        <v>7030312</v>
+        <v>7030329</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123052224</v>
+        <v>123041564</v>
       </c>
       <c r="B30" t="n">
-        <v>90940</v>
+        <v>91397</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,25 +3561,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597309</v>
+        <v>597391</v>
       </c>
       <c r="R30" t="n">
-        <v>7030317</v>
+        <v>7030308</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123041531</v>
+        <v>123044289</v>
       </c>
       <c r="B31" t="n">
-        <v>90940</v>
+        <v>79876</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3663,25 +3663,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597390</v>
+        <v>597317</v>
       </c>
       <c r="R31" t="n">
-        <v>7030296</v>
+        <v>7030322</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123039722</v>
+        <v>123040577</v>
       </c>
       <c r="B32" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597461</v>
+        <v>597442</v>
       </c>
       <c r="R32" t="n">
-        <v>7030329</v>
+        <v>7030306</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123044293</v>
+        <v>123041531</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>90948</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3871,21 +3871,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597316</v>
+        <v>597390</v>
       </c>
       <c r="R33" t="n">
-        <v>7030324</v>
+        <v>7030296</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3960,7 +3960,7 @@
         <v>123071993</v>
       </c>
       <c r="B34" t="n">
-        <v>91605</v>
+        <v>91613</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123045077</v>
+        <v>123042345</v>
       </c>
       <c r="B3" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597313</v>
+        <v>597413</v>
       </c>
       <c r="R3" t="n">
-        <v>7030320</v>
+        <v>7030346</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123042680</v>
+        <v>123045077</v>
       </c>
       <c r="B4" t="n">
-        <v>91243</v>
+        <v>90917</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,25 +905,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597383</v>
+        <v>597313</v>
       </c>
       <c r="R4" t="n">
-        <v>7030347</v>
+        <v>7030320</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123042345</v>
+        <v>123042680</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597413</v>
+        <v>597383</v>
       </c>
       <c r="R5" t="n">
-        <v>7030346</v>
+        <v>7030347</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123041516</v>
+        <v>123041379</v>
       </c>
       <c r="B16" t="n">
-        <v>91397</v>
+        <v>91243</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,25 +2138,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597391</v>
+        <v>597386</v>
       </c>
       <c r="R16" t="n">
-        <v>7030295</v>
+        <v>7030293</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123041379</v>
+        <v>123041516</v>
       </c>
       <c r="B17" t="n">
-        <v>91243</v>
+        <v>91397</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,25 +2240,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597386</v>
+        <v>597391</v>
       </c>
       <c r="R17" t="n">
-        <v>7030293</v>
+        <v>7030295</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123042345</v>
+        <v>123041564</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>91397</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597413</v>
+        <v>597391</v>
       </c>
       <c r="R3" t="n">
-        <v>7030346</v>
+        <v>7030308</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123045077</v>
+        <v>123042937</v>
       </c>
       <c r="B4" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,25 +905,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597313</v>
+        <v>597397</v>
       </c>
       <c r="R4" t="n">
-        <v>7030320</v>
+        <v>7030367</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123042680</v>
+        <v>123044251</v>
       </c>
       <c r="B5" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597383</v>
+        <v>597321</v>
       </c>
       <c r="R5" t="n">
-        <v>7030347</v>
+        <v>7030312</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123041955</v>
+        <v>123044298</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597379</v>
+        <v>597315</v>
       </c>
       <c r="R6" t="n">
-        <v>7030360</v>
+        <v>7030325</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123044251</v>
+        <v>123045077</v>
       </c>
       <c r="B7" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,25 +1211,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597321</v>
+        <v>597313</v>
       </c>
       <c r="R7" t="n">
-        <v>7030312</v>
+        <v>7030320</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123052224</v>
+        <v>123041955</v>
       </c>
       <c r="B8" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597309</v>
+        <v>597379</v>
       </c>
       <c r="R8" t="n">
-        <v>7030317</v>
+        <v>7030360</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123039951</v>
+        <v>123052146</v>
       </c>
       <c r="B9" t="n">
-        <v>90952</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,34 +1419,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597462</v>
+        <v>597309</v>
       </c>
       <c r="R9" t="n">
-        <v>7030312</v>
+        <v>7030317</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,7 +1514,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123050244</v>
+        <v>123049756</v>
       </c>
       <c r="B10" t="n">
         <v>90948</v>
@@ -1545,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597436</v>
+        <v>597344</v>
       </c>
       <c r="R10" t="n">
-        <v>7030329</v>
+        <v>7030297</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1607,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123043079</v>
+        <v>123044316</v>
       </c>
       <c r="B11" t="n">
-        <v>90917</v>
+        <v>79882</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,21 +1632,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597393</v>
+        <v>597313</v>
       </c>
       <c r="R11" t="n">
-        <v>7030365</v>
+        <v>7030320</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123052146</v>
+        <v>123041901</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>90948</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,43 +1734,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597309</v>
+        <v>597380</v>
       </c>
       <c r="R12" t="n">
-        <v>7030317</v>
+        <v>7030371</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1820,7 +1820,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123052262</v>
+        <v>123039722</v>
       </c>
       <c r="B13" t="n">
         <v>90952</v>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597377</v>
+        <v>597461</v>
       </c>
       <c r="R13" t="n">
-        <v>7030279</v>
+        <v>7030329</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123044316</v>
+        <v>123040568</v>
       </c>
       <c r="B14" t="n">
-        <v>79882</v>
+        <v>91397</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,25 +1934,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597313</v>
+        <v>597441</v>
       </c>
       <c r="R14" t="n">
-        <v>7030320</v>
+        <v>7030301</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123044293</v>
+        <v>123051419</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>90948</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2040,21 +2040,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597316</v>
+        <v>597335</v>
       </c>
       <c r="R15" t="n">
-        <v>7030324</v>
+        <v>7030341</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123041379</v>
+        <v>123040637</v>
       </c>
       <c r="B16" t="n">
-        <v>91243</v>
+        <v>91350</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2142,21 +2142,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597386</v>
+        <v>597437</v>
       </c>
       <c r="R16" t="n">
-        <v>7030293</v>
+        <v>7030292</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2228,10 +2223,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123041516</v>
+        <v>123052224</v>
       </c>
       <c r="B17" t="n">
-        <v>91397</v>
+        <v>90948</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,25 +2235,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597391</v>
+        <v>597309</v>
       </c>
       <c r="R17" t="n">
-        <v>7030295</v>
+        <v>7030317</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2330,10 +2325,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123040637</v>
+        <v>123039951</v>
       </c>
       <c r="B18" t="n">
-        <v>91350</v>
+        <v>90952</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2346,16 +2341,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597437</v>
+        <v>597462</v>
       </c>
       <c r="R18" t="n">
-        <v>7030292</v>
+        <v>7030312</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123041901</v>
+        <v>123041531</v>
       </c>
       <c r="B19" t="n">
         <v>90948</v>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597380</v>
+        <v>597390</v>
       </c>
       <c r="R19" t="n">
-        <v>7030371</v>
+        <v>7030296</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2529,10 +2529,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123044298</v>
+        <v>123052262</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2545,21 +2545,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597315</v>
+        <v>597377</v>
       </c>
       <c r="R20" t="n">
-        <v>7030325</v>
+        <v>7030279</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2631,7 +2631,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123041496</v>
+        <v>123040577</v>
       </c>
       <c r="B21" t="n">
         <v>90952</v>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597392</v>
+        <v>597442</v>
       </c>
       <c r="R21" t="n">
-        <v>7030296</v>
+        <v>7030306</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123042937</v>
+        <v>123043079</v>
       </c>
       <c r="B22" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2745,25 +2745,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597397</v>
+        <v>597393</v>
       </c>
       <c r="R22" t="n">
-        <v>7030367</v>
+        <v>7030365</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123051419</v>
+        <v>123041496</v>
       </c>
       <c r="B23" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2851,21 +2851,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597335</v>
+        <v>597392</v>
       </c>
       <c r="R23" t="n">
-        <v>7030341</v>
+        <v>7030296</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123043324</v>
+        <v>123041379</v>
       </c>
       <c r="B24" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2953,21 +2953,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597342</v>
+        <v>597386</v>
       </c>
       <c r="R24" t="n">
-        <v>7030326</v>
+        <v>7030293</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123039792</v>
+        <v>123041516</v>
       </c>
       <c r="B25" t="n">
-        <v>91243</v>
+        <v>91397</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3051,25 +3051,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597458</v>
+        <v>597391</v>
       </c>
       <c r="R25" t="n">
-        <v>7030292</v>
+        <v>7030295</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123041570</v>
+        <v>123042345</v>
       </c>
       <c r="B26" t="n">
         <v>90952</v>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597395</v>
+        <v>597413</v>
       </c>
       <c r="R26" t="n">
-        <v>7030312</v>
+        <v>7030346</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123040568</v>
+        <v>123050244</v>
       </c>
       <c r="B27" t="n">
-        <v>91397</v>
+        <v>90948</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3255,25 +3255,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597441</v>
+        <v>597436</v>
       </c>
       <c r="R27" t="n">
-        <v>7030301</v>
+        <v>7030329</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3345,10 +3345,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123049756</v>
+        <v>123044293</v>
       </c>
       <c r="B28" t="n">
-        <v>90948</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597344</v>
+        <v>597316</v>
       </c>
       <c r="R28" t="n">
-        <v>7030297</v>
+        <v>7030324</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123039722</v>
+        <v>123039792</v>
       </c>
       <c r="B29" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597461</v>
+        <v>597458</v>
       </c>
       <c r="R29" t="n">
-        <v>7030329</v>
+        <v>7030292</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123041564</v>
+        <v>123041570</v>
       </c>
       <c r="B30" t="n">
-        <v>91397</v>
+        <v>90952</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,25 +3561,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597391</v>
+        <v>597395</v>
       </c>
       <c r="R30" t="n">
-        <v>7030308</v>
+        <v>7030312</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123044289</v>
+        <v>123043324</v>
       </c>
       <c r="B31" t="n">
-        <v>79876</v>
+        <v>90952</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3663,25 +3663,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597317</v>
+        <v>597342</v>
       </c>
       <c r="R31" t="n">
-        <v>7030322</v>
+        <v>7030326</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123040577</v>
+        <v>123042680</v>
       </c>
       <c r="B32" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3769,21 +3769,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597442</v>
+        <v>597383</v>
       </c>
       <c r="R32" t="n">
-        <v>7030306</v>
+        <v>7030347</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123041531</v>
+        <v>123044289</v>
       </c>
       <c r="B33" t="n">
-        <v>90948</v>
+        <v>79876</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3867,25 +3867,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597390</v>
+        <v>597317</v>
       </c>
       <c r="R33" t="n">
-        <v>7030296</v>
+        <v>7030322</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123052146</v>
+        <v>123049756</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>90948</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,43 +1419,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597309</v>
+        <v>597344</v>
       </c>
       <c r="R9" t="n">
-        <v>7030317</v>
+        <v>7030297</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1514,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123049756</v>
+        <v>123052146</v>
       </c>
       <c r="B10" t="n">
-        <v>90948</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1530,34 +1521,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597344</v>
+        <v>597309</v>
       </c>
       <c r="R10" t="n">
-        <v>7030297</v>
+        <v>7030317</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123049756</v>
+        <v>123052146</v>
       </c>
       <c r="B9" t="n">
-        <v>90948</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,34 +1419,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597344</v>
+        <v>597309</v>
       </c>
       <c r="R9" t="n">
-        <v>7030297</v>
+        <v>7030317</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123052146</v>
+        <v>123049756</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>90948</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,43 +1530,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597309</v>
+        <v>597344</v>
       </c>
       <c r="R10" t="n">
-        <v>7030317</v>
+        <v>7030297</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -3141,10 +3141,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123042345</v>
+        <v>123050244</v>
       </c>
       <c r="B26" t="n">
-        <v>90952</v>
+        <v>90948</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3157,21 +3157,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597413</v>
+        <v>597436</v>
       </c>
       <c r="R26" t="n">
-        <v>7030346</v>
+        <v>7030329</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123050244</v>
+        <v>123042345</v>
       </c>
       <c r="B27" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3259,21 +3259,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597436</v>
+        <v>597413</v>
       </c>
       <c r="R27" t="n">
-        <v>7030329</v>
+        <v>7030346</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123041564</v>
+        <v>123040568</v>
       </c>
       <c r="B3" t="n">
         <v>91397</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597391</v>
+        <v>597441</v>
       </c>
       <c r="R3" t="n">
-        <v>7030308</v>
+        <v>7030301</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123042937</v>
+        <v>123050244</v>
       </c>
       <c r="B4" t="n">
-        <v>90952</v>
+        <v>90948</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597397</v>
+        <v>597436</v>
       </c>
       <c r="R4" t="n">
-        <v>7030367</v>
+        <v>7030329</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123044251</v>
+        <v>123044316</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>79882</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,25 +1007,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597321</v>
+        <v>597313</v>
       </c>
       <c r="R5" t="n">
-        <v>7030312</v>
+        <v>7030320</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123044298</v>
+        <v>123045077</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,25 +1109,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597315</v>
+        <v>597313</v>
       </c>
       <c r="R6" t="n">
-        <v>7030325</v>
+        <v>7030320</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123045077</v>
+        <v>123041496</v>
       </c>
       <c r="B7" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,25 +1211,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597313</v>
+        <v>597392</v>
       </c>
       <c r="R7" t="n">
-        <v>7030320</v>
+        <v>7030296</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123041955</v>
+        <v>123042937</v>
       </c>
       <c r="B8" t="n">
         <v>90952</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597379</v>
+        <v>597397</v>
       </c>
       <c r="R8" t="n">
-        <v>7030360</v>
+        <v>7030367</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123052146</v>
+        <v>123042680</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>91243</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,43 +1419,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597309</v>
+        <v>597383</v>
       </c>
       <c r="R9" t="n">
-        <v>7030317</v>
+        <v>7030347</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1514,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123049756</v>
+        <v>123043324</v>
       </c>
       <c r="B10" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1530,21 +1521,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597344</v>
+        <v>597342</v>
       </c>
       <c r="R10" t="n">
-        <v>7030297</v>
+        <v>7030326</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1616,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123044316</v>
+        <v>123039951</v>
       </c>
       <c r="B11" t="n">
-        <v>79882</v>
+        <v>90952</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,25 +1619,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1656,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597313</v>
+        <v>597462</v>
       </c>
       <c r="R11" t="n">
-        <v>7030320</v>
+        <v>7030312</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1718,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123041901</v>
+        <v>123052146</v>
       </c>
       <c r="B12" t="n">
-        <v>90948</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,34 +1725,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597380</v>
+        <v>597309</v>
       </c>
       <c r="R12" t="n">
-        <v>7030371</v>
+        <v>7030317</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1820,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123039722</v>
+        <v>123044298</v>
       </c>
       <c r="B13" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,21 +1836,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597461</v>
+        <v>597315</v>
       </c>
       <c r="R13" t="n">
-        <v>7030329</v>
+        <v>7030325</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123040568</v>
+        <v>123044289</v>
       </c>
       <c r="B14" t="n">
-        <v>91397</v>
+        <v>79876</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,25 +1934,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597441</v>
+        <v>597317</v>
       </c>
       <c r="R14" t="n">
-        <v>7030301</v>
+        <v>7030322</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123051419</v>
+        <v>123049756</v>
       </c>
       <c r="B15" t="n">
         <v>90948</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597335</v>
+        <v>597344</v>
       </c>
       <c r="R15" t="n">
-        <v>7030341</v>
+        <v>7030297</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123040637</v>
+        <v>123041901</v>
       </c>
       <c r="B16" t="n">
-        <v>91350</v>
+        <v>90948</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2142,16 +2142,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040186</v>
+        <v>1108</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2161,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597437</v>
+        <v>597380</v>
       </c>
       <c r="R16" t="n">
-        <v>7030292</v>
+        <v>7030371</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2223,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123052224</v>
+        <v>123041564</v>
       </c>
       <c r="B17" t="n">
-        <v>90948</v>
+        <v>91397</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,25 +2240,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2263,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597309</v>
+        <v>597391</v>
       </c>
       <c r="R17" t="n">
-        <v>7030317</v>
+        <v>7030308</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2325,7 +2330,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123039951</v>
+        <v>123041955</v>
       </c>
       <c r="B18" t="n">
         <v>90952</v>
@@ -2365,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597462</v>
+        <v>597379</v>
       </c>
       <c r="R18" t="n">
-        <v>7030312</v>
+        <v>7030360</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2427,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123041531</v>
+        <v>123052262</v>
       </c>
       <c r="B19" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2443,21 +2448,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597390</v>
+        <v>597377</v>
       </c>
       <c r="R19" t="n">
-        <v>7030296</v>
+        <v>7030279</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2529,7 +2534,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123052262</v>
+        <v>123044251</v>
       </c>
       <c r="B20" t="n">
         <v>90952</v>
@@ -2569,10 +2574,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597377</v>
+        <v>597321</v>
       </c>
       <c r="R20" t="n">
-        <v>7030279</v>
+        <v>7030312</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2631,7 +2636,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123040577</v>
+        <v>123042345</v>
       </c>
       <c r="B21" t="n">
         <v>90952</v>
@@ -2671,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597442</v>
+        <v>597413</v>
       </c>
       <c r="R21" t="n">
-        <v>7030306</v>
+        <v>7030346</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2835,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123041496</v>
+        <v>123039792</v>
       </c>
       <c r="B23" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2851,21 +2856,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2880,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597392</v>
+        <v>597458</v>
       </c>
       <c r="R23" t="n">
-        <v>7030296</v>
+        <v>7030292</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2937,10 +2942,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123041379</v>
+        <v>123039722</v>
       </c>
       <c r="B24" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2953,21 +2958,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2977,10 +2982,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597386</v>
+        <v>597461</v>
       </c>
       <c r="R24" t="n">
-        <v>7030293</v>
+        <v>7030329</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3039,10 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123041516</v>
+        <v>123040637</v>
       </c>
       <c r="B25" t="n">
-        <v>91397</v>
+        <v>91350</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3051,25 +3056,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597391</v>
+        <v>597437</v>
       </c>
       <c r="R25" t="n">
-        <v>7030295</v>
+        <v>7030292</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123050244</v>
+        <v>123041531</v>
       </c>
       <c r="B26" t="n">
         <v>90948</v>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597436</v>
+        <v>597390</v>
       </c>
       <c r="R26" t="n">
-        <v>7030329</v>
+        <v>7030296</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123042345</v>
+        <v>123044293</v>
       </c>
       <c r="B27" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3259,21 +3259,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597413</v>
+        <v>597316</v>
       </c>
       <c r="R27" t="n">
-        <v>7030346</v>
+        <v>7030324</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3345,10 +3345,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123044293</v>
+        <v>123040577</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597316</v>
+        <v>597442</v>
       </c>
       <c r="R28" t="n">
-        <v>7030324</v>
+        <v>7030306</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123039792</v>
+        <v>123041516</v>
       </c>
       <c r="B29" t="n">
-        <v>91243</v>
+        <v>91397</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3459,25 +3459,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597458</v>
+        <v>597391</v>
       </c>
       <c r="R29" t="n">
-        <v>7030292</v>
+        <v>7030295</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123041570</v>
+        <v>123051419</v>
       </c>
       <c r="B30" t="n">
-        <v>90952</v>
+        <v>90948</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597395</v>
+        <v>597335</v>
       </c>
       <c r="R30" t="n">
-        <v>7030312</v>
+        <v>7030341</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123043324</v>
+        <v>123052224</v>
       </c>
       <c r="B31" t="n">
-        <v>90952</v>
+        <v>90948</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597342</v>
+        <v>597309</v>
       </c>
       <c r="R31" t="n">
-        <v>7030326</v>
+        <v>7030317</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123042680</v>
+        <v>123041379</v>
       </c>
       <c r="B32" t="n">
         <v>91243</v>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597383</v>
+        <v>597386</v>
       </c>
       <c r="R32" t="n">
-        <v>7030347</v>
+        <v>7030293</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123044289</v>
+        <v>123041570</v>
       </c>
       <c r="B33" t="n">
-        <v>79876</v>
+        <v>90952</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3867,25 +3867,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597317</v>
+        <v>597395</v>
       </c>
       <c r="R33" t="n">
-        <v>7030322</v>
+        <v>7030312</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123040568</v>
+        <v>123040637</v>
       </c>
       <c r="B3" t="n">
-        <v>91397</v>
+        <v>91350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597441</v>
+        <v>597437</v>
       </c>
       <c r="R3" t="n">
-        <v>7030301</v>
+        <v>7030292</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123050244</v>
+        <v>123044289</v>
       </c>
       <c r="B4" t="n">
-        <v>90948</v>
+        <v>79876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597436</v>
+        <v>597317</v>
       </c>
       <c r="R4" t="n">
-        <v>7030329</v>
+        <v>7030322</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123044316</v>
+        <v>123051419</v>
       </c>
       <c r="B5" t="n">
-        <v>79882</v>
+        <v>90948</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597313</v>
+        <v>597335</v>
       </c>
       <c r="R5" t="n">
-        <v>7030320</v>
+        <v>7030341</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1097,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123045077</v>
+        <v>123041379</v>
       </c>
       <c r="B6" t="n">
-        <v>90917</v>
+        <v>91243</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597313</v>
+        <v>597386</v>
       </c>
       <c r="R6" t="n">
-        <v>7030320</v>
+        <v>7030293</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1199,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123041496</v>
+        <v>123041531</v>
       </c>
       <c r="B7" t="n">
-        <v>90952</v>
+        <v>90948</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1210,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,7 +1234,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597392</v>
+        <v>597390</v>
       </c>
       <c r="R7" t="n">
         <v>7030296</v>
@@ -1301,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123042937</v>
+        <v>123040568</v>
       </c>
       <c r="B8" t="n">
-        <v>90952</v>
+        <v>91397</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597397</v>
+        <v>597441</v>
       </c>
       <c r="R8" t="n">
-        <v>7030367</v>
+        <v>7030301</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1403,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123042680</v>
+        <v>123044293</v>
       </c>
       <c r="B9" t="n">
-        <v>91243</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597383</v>
+        <v>597316</v>
       </c>
       <c r="R9" t="n">
-        <v>7030347</v>
+        <v>7030324</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123043324</v>
+        <v>123044298</v>
       </c>
       <c r="B10" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597342</v>
+        <v>597315</v>
       </c>
       <c r="R10" t="n">
-        <v>7030326</v>
+        <v>7030325</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1607,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123039951</v>
+        <v>123050244</v>
       </c>
       <c r="B11" t="n">
-        <v>90952</v>
+        <v>90948</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,21 +1618,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597462</v>
+        <v>597436</v>
       </c>
       <c r="R11" t="n">
-        <v>7030312</v>
+        <v>7030329</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123052146</v>
+        <v>123042680</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>91243</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,43 +1720,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597309</v>
+        <v>597383</v>
       </c>
       <c r="R12" t="n">
-        <v>7030317</v>
+        <v>7030347</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1820,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123044298</v>
+        <v>123039951</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1860,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597315</v>
+        <v>597462</v>
       </c>
       <c r="R13" t="n">
-        <v>7030325</v>
+        <v>7030312</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1922,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123044289</v>
+        <v>123049756</v>
       </c>
       <c r="B14" t="n">
-        <v>79876</v>
+        <v>90948</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,25 +1920,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1962,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597317</v>
+        <v>597344</v>
       </c>
       <c r="R14" t="n">
-        <v>7030322</v>
+        <v>7030297</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2024,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123049756</v>
+        <v>123041570</v>
       </c>
       <c r="B15" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2040,21 +2026,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2064,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597344</v>
+        <v>597395</v>
       </c>
       <c r="R15" t="n">
-        <v>7030297</v>
+        <v>7030312</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2126,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123041901</v>
+        <v>123042937</v>
       </c>
       <c r="B16" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2142,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597380</v>
+        <v>597397</v>
       </c>
       <c r="R16" t="n">
-        <v>7030371</v>
+        <v>7030367</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2228,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123041564</v>
+        <v>123041901</v>
       </c>
       <c r="B17" t="n">
-        <v>91397</v>
+        <v>90948</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,25 +2226,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597391</v>
+        <v>597380</v>
       </c>
       <c r="R17" t="n">
-        <v>7030308</v>
+        <v>7030371</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2330,7 +2316,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123041955</v>
+        <v>123040577</v>
       </c>
       <c r="B18" t="n">
         <v>90952</v>
@@ -2370,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597379</v>
+        <v>597442</v>
       </c>
       <c r="R18" t="n">
-        <v>7030360</v>
+        <v>7030306</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2432,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123052262</v>
+        <v>123039792</v>
       </c>
       <c r="B19" t="n">
-        <v>90952</v>
+        <v>91243</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2448,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2472,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597377</v>
+        <v>597458</v>
       </c>
       <c r="R19" t="n">
-        <v>7030279</v>
+        <v>7030292</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2534,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123044251</v>
+        <v>123045077</v>
       </c>
       <c r="B20" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,25 +2532,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597321</v>
+        <v>597313</v>
       </c>
       <c r="R20" t="n">
-        <v>7030312</v>
+        <v>7030320</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2636,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123042345</v>
+        <v>123052224</v>
       </c>
       <c r="B21" t="n">
-        <v>90952</v>
+        <v>90948</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2652,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2676,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597413</v>
+        <v>597309</v>
       </c>
       <c r="R21" t="n">
-        <v>7030346</v>
+        <v>7030317</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2738,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123043079</v>
+        <v>123044316</v>
       </c>
       <c r="B22" t="n">
-        <v>90917</v>
+        <v>79882</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2754,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597393</v>
+        <v>597313</v>
       </c>
       <c r="R22" t="n">
-        <v>7030365</v>
+        <v>7030320</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2840,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123039792</v>
+        <v>123041496</v>
       </c>
       <c r="B23" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2856,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2880,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597458</v>
+        <v>597392</v>
       </c>
       <c r="R23" t="n">
-        <v>7030292</v>
+        <v>7030296</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2942,7 +2928,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123039722</v>
+        <v>123041955</v>
       </c>
       <c r="B24" t="n">
         <v>90952</v>
@@ -2982,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597461</v>
+        <v>597379</v>
       </c>
       <c r="R24" t="n">
-        <v>7030329</v>
+        <v>7030360</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3044,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123040637</v>
+        <v>123043324</v>
       </c>
       <c r="B25" t="n">
-        <v>91350</v>
+        <v>90952</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3060,16 +3046,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597437</v>
+        <v>597342</v>
       </c>
       <c r="R25" t="n">
-        <v>7030292</v>
+        <v>7030326</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3141,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123041531</v>
+        <v>123043079</v>
       </c>
       <c r="B26" t="n">
-        <v>90948</v>
+        <v>90917</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3153,25 +3144,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597390</v>
+        <v>597393</v>
       </c>
       <c r="R26" t="n">
-        <v>7030296</v>
+        <v>7030365</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3243,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123044293</v>
+        <v>123039722</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3259,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3283,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597316</v>
+        <v>597461</v>
       </c>
       <c r="R27" t="n">
-        <v>7030324</v>
+        <v>7030329</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3345,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123040577</v>
+        <v>123041564</v>
       </c>
       <c r="B28" t="n">
-        <v>90952</v>
+        <v>91397</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3357,25 +3348,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3385,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597442</v>
+        <v>597391</v>
       </c>
       <c r="R28" t="n">
-        <v>7030306</v>
+        <v>7030308</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3447,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123041516</v>
+        <v>123052146</v>
       </c>
       <c r="B29" t="n">
-        <v>91397</v>
+        <v>57631</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3459,38 +3450,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597391</v>
+        <v>597309</v>
       </c>
       <c r="R29" t="n">
-        <v>7030295</v>
+        <v>7030317</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123051419</v>
+        <v>123041516</v>
       </c>
       <c r="B30" t="n">
-        <v>90948</v>
+        <v>91397</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,25 +3561,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597335</v>
+        <v>597391</v>
       </c>
       <c r="R30" t="n">
-        <v>7030341</v>
+        <v>7030295</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123052224</v>
+        <v>123044251</v>
       </c>
       <c r="B31" t="n">
-        <v>90948</v>
+        <v>90952</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597309</v>
+        <v>597321</v>
       </c>
       <c r="R31" t="n">
-        <v>7030317</v>
+        <v>7030312</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123041379</v>
+        <v>123052262</v>
       </c>
       <c r="B32" t="n">
-        <v>91243</v>
+        <v>90952</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3769,21 +3769,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597386</v>
+        <v>597377</v>
       </c>
       <c r="R32" t="n">
-        <v>7030293</v>
+        <v>7030279</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3855,7 +3855,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123041570</v>
+        <v>123042345</v>
       </c>
       <c r="B33" t="n">
         <v>90952</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597395</v>
+        <v>597413</v>
       </c>
       <c r="R33" t="n">
-        <v>7030312</v>
+        <v>7030346</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123051419</v>
+        <v>123041379</v>
       </c>
       <c r="B5" t="n">
-        <v>90948</v>
+        <v>91243</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597335</v>
+        <v>597386</v>
       </c>
       <c r="R5" t="n">
-        <v>7030341</v>
+        <v>7030293</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123041379</v>
+        <v>123041531</v>
       </c>
       <c r="B6" t="n">
-        <v>91243</v>
+        <v>90948</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597386</v>
+        <v>597390</v>
       </c>
       <c r="R6" t="n">
-        <v>7030293</v>
+        <v>7030296</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123041531</v>
+        <v>123040568</v>
       </c>
       <c r="B7" t="n">
-        <v>90948</v>
+        <v>91397</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597390</v>
+        <v>597441</v>
       </c>
       <c r="R7" t="n">
-        <v>7030296</v>
+        <v>7030301</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123040568</v>
+        <v>123044293</v>
       </c>
       <c r="B8" t="n">
-        <v>91397</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597441</v>
+        <v>597316</v>
       </c>
       <c r="R8" t="n">
-        <v>7030301</v>
+        <v>7030324</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123044293</v>
+        <v>123044298</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597316</v>
+        <v>597315</v>
       </c>
       <c r="R9" t="n">
-        <v>7030324</v>
+        <v>7030325</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123044298</v>
+        <v>123051419</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>90948</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597315</v>
+        <v>597335</v>
       </c>
       <c r="R10" t="n">
-        <v>7030325</v>
+        <v>7030341</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123041379</v>
+        <v>123051419</v>
       </c>
       <c r="B5" t="n">
-        <v>91243</v>
+        <v>90948</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597386</v>
+        <v>597335</v>
       </c>
       <c r="R5" t="n">
-        <v>7030293</v>
+        <v>7030341</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123041531</v>
+        <v>123041379</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
+        <v>91243</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597390</v>
+        <v>597386</v>
       </c>
       <c r="R6" t="n">
-        <v>7030296</v>
+        <v>7030293</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123040568</v>
+        <v>123041531</v>
       </c>
       <c r="B7" t="n">
-        <v>91397</v>
+        <v>90948</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597441</v>
+        <v>597390</v>
       </c>
       <c r="R7" t="n">
-        <v>7030301</v>
+        <v>7030296</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123044293</v>
+        <v>123040568</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>91397</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1308,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597316</v>
+        <v>597441</v>
       </c>
       <c r="R8" t="n">
-        <v>7030324</v>
+        <v>7030301</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123044298</v>
+        <v>123044293</v>
       </c>
       <c r="B9" t="n">
         <v>79847</v>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597315</v>
+        <v>597316</v>
       </c>
       <c r="R9" t="n">
-        <v>7030325</v>
+        <v>7030324</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123051419</v>
+        <v>123044298</v>
       </c>
       <c r="B10" t="n">
-        <v>90948</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597335</v>
+        <v>597315</v>
       </c>
       <c r="R10" t="n">
-        <v>7030341</v>
+        <v>7030325</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123040637</v>
+        <v>123042345</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>90955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597437</v>
+        <v>597413</v>
       </c>
       <c r="R3" t="n">
-        <v>7030292</v>
+        <v>7030346</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123044289</v>
+        <v>123044251</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>90955</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +905,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597317</v>
+        <v>597321</v>
       </c>
       <c r="R4" t="n">
-        <v>7030322</v>
+        <v>7030312</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -990,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123041379</v>
+        <v>123042937</v>
       </c>
       <c r="B5" t="n">
-        <v>91243</v>
+        <v>90955</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597386</v>
+        <v>597397</v>
       </c>
       <c r="R5" t="n">
-        <v>7030293</v>
+        <v>7030367</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123041531</v>
+        <v>123040637</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
+        <v>91353</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,21 +1113,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597390</v>
+        <v>597437</v>
       </c>
       <c r="R6" t="n">
-        <v>7030296</v>
+        <v>7030292</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123040568</v>
+        <v>123052224</v>
       </c>
       <c r="B7" t="n">
-        <v>91397</v>
+        <v>90951</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597441</v>
+        <v>597309</v>
       </c>
       <c r="R7" t="n">
-        <v>7030301</v>
+        <v>7030317</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123044293</v>
+        <v>123042680</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>91242</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597316</v>
+        <v>597383</v>
       </c>
       <c r="R8" t="n">
-        <v>7030324</v>
+        <v>7030347</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123044298</v>
+        <v>123045077</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>90920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597315</v>
+        <v>597313</v>
       </c>
       <c r="R9" t="n">
-        <v>7030325</v>
+        <v>7030320</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123051419</v>
+        <v>123044298</v>
       </c>
       <c r="B10" t="n">
-        <v>90948</v>
+        <v>79850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597335</v>
+        <v>597315</v>
       </c>
       <c r="R10" t="n">
-        <v>7030341</v>
+        <v>7030325</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123050244</v>
+        <v>123044316</v>
       </c>
       <c r="B11" t="n">
-        <v>90948</v>
+        <v>79885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597436</v>
+        <v>597313</v>
       </c>
       <c r="R11" t="n">
-        <v>7030329</v>
+        <v>7030320</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123042680</v>
+        <v>123041901</v>
       </c>
       <c r="B12" t="n">
-        <v>91243</v>
+        <v>90951</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597383</v>
+        <v>597380</v>
       </c>
       <c r="R12" t="n">
-        <v>7030347</v>
+        <v>7030371</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123039951</v>
+        <v>123041516</v>
       </c>
       <c r="B13" t="n">
-        <v>90952</v>
+        <v>91400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1818,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597462</v>
+        <v>597391</v>
       </c>
       <c r="R13" t="n">
-        <v>7030312</v>
+        <v>7030295</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123049756</v>
+        <v>123039722</v>
       </c>
       <c r="B14" t="n">
-        <v>90948</v>
+        <v>90955</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597344</v>
+        <v>597461</v>
       </c>
       <c r="R14" t="n">
-        <v>7030297</v>
+        <v>7030329</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2013,7 +2013,7 @@
         <v>123041570</v>
       </c>
       <c r="B15" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123042937</v>
+        <v>123043079</v>
       </c>
       <c r="B16" t="n">
-        <v>90952</v>
+        <v>90920</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,25 +2124,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597397</v>
+        <v>597393</v>
       </c>
       <c r="R16" t="n">
-        <v>7030367</v>
+        <v>7030365</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123041901</v>
+        <v>123040577</v>
       </c>
       <c r="B17" t="n">
-        <v>90948</v>
+        <v>90955</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2230,21 +2230,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2254,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597380</v>
+        <v>597442</v>
       </c>
       <c r="R17" t="n">
-        <v>7030371</v>
+        <v>7030306</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123040577</v>
+        <v>123039951</v>
       </c>
       <c r="B18" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597442</v>
+        <v>597462</v>
       </c>
       <c r="R18" t="n">
-        <v>7030306</v>
+        <v>7030312</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123039792</v>
+        <v>123041531</v>
       </c>
       <c r="B19" t="n">
-        <v>91243</v>
+        <v>90951</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597458</v>
+        <v>597390</v>
       </c>
       <c r="R19" t="n">
-        <v>7030292</v>
+        <v>7030296</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123045077</v>
+        <v>123039792</v>
       </c>
       <c r="B20" t="n">
-        <v>90917</v>
+        <v>91242</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,25 +2532,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597313</v>
+        <v>597458</v>
       </c>
       <c r="R20" t="n">
-        <v>7030320</v>
+        <v>7030292</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123052224</v>
+        <v>123050244</v>
       </c>
       <c r="B21" t="n">
-        <v>90948</v>
+        <v>90951</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597309</v>
+        <v>597436</v>
       </c>
       <c r="R21" t="n">
-        <v>7030317</v>
+        <v>7030329</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123044316</v>
+        <v>123052146</v>
       </c>
       <c r="B22" t="n">
-        <v>79882</v>
+        <v>57634</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2736,38 +2736,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597313</v>
+        <v>597309</v>
       </c>
       <c r="R22" t="n">
-        <v>7030320</v>
+        <v>7030317</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2826,10 +2835,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123041496</v>
+        <v>123041564</v>
       </c>
       <c r="B23" t="n">
-        <v>90952</v>
+        <v>91400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2838,25 +2847,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2875,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597392</v>
+        <v>597391</v>
       </c>
       <c r="R23" t="n">
-        <v>7030296</v>
+        <v>7030308</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2928,10 +2937,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123041955</v>
+        <v>123041379</v>
       </c>
       <c r="B24" t="n">
-        <v>90952</v>
+        <v>91242</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2944,21 +2953,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2968,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597379</v>
+        <v>597386</v>
       </c>
       <c r="R24" t="n">
-        <v>7030360</v>
+        <v>7030293</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3033,7 +3042,7 @@
         <v>123043324</v>
       </c>
       <c r="B25" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,10 +3141,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123043079</v>
+        <v>123041955</v>
       </c>
       <c r="B26" t="n">
-        <v>90917</v>
+        <v>90955</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,25 +3153,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597393</v>
+        <v>597379</v>
       </c>
       <c r="R26" t="n">
-        <v>7030365</v>
+        <v>7030360</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3234,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123039722</v>
+        <v>123040568</v>
       </c>
       <c r="B27" t="n">
-        <v>90952</v>
+        <v>91400</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,25 +3255,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597461</v>
+        <v>597441</v>
       </c>
       <c r="R27" t="n">
-        <v>7030329</v>
+        <v>7030301</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3336,10 +3345,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123041564</v>
+        <v>123044293</v>
       </c>
       <c r="B28" t="n">
-        <v>91397</v>
+        <v>79850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3348,25 +3357,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3385,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597391</v>
+        <v>597316</v>
       </c>
       <c r="R28" t="n">
-        <v>7030308</v>
+        <v>7030324</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3438,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123052146</v>
+        <v>123044289</v>
       </c>
       <c r="B29" t="n">
-        <v>57631</v>
+        <v>79879</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3450,47 +3459,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597309</v>
+        <v>597317</v>
       </c>
       <c r="R29" t="n">
-        <v>7030317</v>
+        <v>7030322</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123041516</v>
+        <v>123052262</v>
       </c>
       <c r="B30" t="n">
-        <v>91397</v>
+        <v>90955</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,25 +3561,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597391</v>
+        <v>597377</v>
       </c>
       <c r="R30" t="n">
-        <v>7030295</v>
+        <v>7030279</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123044251</v>
+        <v>123041496</v>
       </c>
       <c r="B31" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597321</v>
+        <v>597392</v>
       </c>
       <c r="R31" t="n">
-        <v>7030312</v>
+        <v>7030296</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123052262</v>
+        <v>123049756</v>
       </c>
       <c r="B32" t="n">
-        <v>90952</v>
+        <v>90951</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3769,21 +3769,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597377</v>
+        <v>597344</v>
       </c>
       <c r="R32" t="n">
-        <v>7030279</v>
+        <v>7030297</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123042345</v>
+        <v>123051419</v>
       </c>
       <c r="B33" t="n">
-        <v>90952</v>
+        <v>90951</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3871,21 +3871,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597413</v>
+        <v>597335</v>
       </c>
       <c r="R33" t="n">
-        <v>7030346</v>
+        <v>7030341</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3960,7 +3960,7 @@
         <v>123071993</v>
       </c>
       <c r="B34" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123042345</v>
+        <v>123042680</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>91244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597413</v>
+        <v>597383</v>
       </c>
       <c r="R3" t="n">
-        <v>7030346</v>
+        <v>7030347</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -896,7 +896,7 @@
         <v>123044251</v>
       </c>
       <c r="B4" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123042937</v>
+        <v>123041379</v>
       </c>
       <c r="B5" t="n">
-        <v>90955</v>
+        <v>91244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597397</v>
+        <v>597386</v>
       </c>
       <c r="R5" t="n">
-        <v>7030367</v>
+        <v>7030293</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123040637</v>
+        <v>123039951</v>
       </c>
       <c r="B6" t="n">
-        <v>91353</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,16 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597437</v>
+        <v>597462</v>
       </c>
       <c r="R6" t="n">
-        <v>7030292</v>
+        <v>7030312</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123052224</v>
+        <v>123040577</v>
       </c>
       <c r="B7" t="n">
-        <v>90951</v>
+        <v>90957</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597309</v>
+        <v>597442</v>
       </c>
       <c r="R7" t="n">
-        <v>7030317</v>
+        <v>7030306</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123042680</v>
+        <v>123041955</v>
       </c>
       <c r="B8" t="n">
-        <v>91242</v>
+        <v>90957</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597383</v>
+        <v>597379</v>
       </c>
       <c r="R8" t="n">
-        <v>7030347</v>
+        <v>7030360</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1398,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123045077</v>
+        <v>123040568</v>
       </c>
       <c r="B9" t="n">
-        <v>90920</v>
+        <v>91402</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1415,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597313</v>
+        <v>597441</v>
       </c>
       <c r="R9" t="n">
-        <v>7030320</v>
+        <v>7030301</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1500,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123044298</v>
+        <v>123043079</v>
       </c>
       <c r="B10" t="n">
-        <v>79850</v>
+        <v>90922</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,25 +1517,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597315</v>
+        <v>597393</v>
       </c>
       <c r="R10" t="n">
-        <v>7030325</v>
+        <v>7030365</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1602,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123044316</v>
+        <v>123050244</v>
       </c>
       <c r="B11" t="n">
-        <v>79885</v>
+        <v>90953</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1619,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597313</v>
+        <v>597436</v>
       </c>
       <c r="R11" t="n">
-        <v>7030320</v>
+        <v>7030329</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1704,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123041901</v>
+        <v>123042937</v>
       </c>
       <c r="B12" t="n">
-        <v>90951</v>
+        <v>90957</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,21 +1725,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597380</v>
+        <v>597397</v>
       </c>
       <c r="R12" t="n">
-        <v>7030371</v>
+        <v>7030367</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1806,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123041516</v>
+        <v>123051419</v>
       </c>
       <c r="B13" t="n">
-        <v>91400</v>
+        <v>90953</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,25 +1823,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597391</v>
+        <v>597335</v>
       </c>
       <c r="R13" t="n">
-        <v>7030295</v>
+        <v>7030341</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1908,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123039722</v>
+        <v>123044298</v>
       </c>
       <c r="B14" t="n">
-        <v>90955</v>
+        <v>79852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1924,21 +1929,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597461</v>
+        <v>597315</v>
       </c>
       <c r="R14" t="n">
-        <v>7030329</v>
+        <v>7030325</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2010,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123041570</v>
+        <v>123042345</v>
       </c>
       <c r="B15" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2050,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597395</v>
+        <v>597413</v>
       </c>
       <c r="R15" t="n">
-        <v>7030312</v>
+        <v>7030346</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2112,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123043079</v>
+        <v>123052146</v>
       </c>
       <c r="B16" t="n">
-        <v>90920</v>
+        <v>57634</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,38 +2129,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597393</v>
+        <v>597309</v>
       </c>
       <c r="R16" t="n">
-        <v>7030365</v>
+        <v>7030317</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2214,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123040577</v>
+        <v>123043324</v>
       </c>
       <c r="B17" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2254,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597442</v>
+        <v>597342</v>
       </c>
       <c r="R17" t="n">
-        <v>7030306</v>
+        <v>7030326</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2316,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123039951</v>
+        <v>123049756</v>
       </c>
       <c r="B18" t="n">
-        <v>90955</v>
+        <v>90953</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2346,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597462</v>
+        <v>597344</v>
       </c>
       <c r="R18" t="n">
-        <v>7030312</v>
+        <v>7030297</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2418,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123041531</v>
+        <v>123041901</v>
       </c>
       <c r="B19" t="n">
-        <v>90951</v>
+        <v>90953</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2458,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597390</v>
+        <v>597380</v>
       </c>
       <c r="R19" t="n">
-        <v>7030296</v>
+        <v>7030371</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2523,7 +2537,7 @@
         <v>123039792</v>
       </c>
       <c r="B20" t="n">
-        <v>91242</v>
+        <v>91244</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123050244</v>
+        <v>123041516</v>
       </c>
       <c r="B21" t="n">
-        <v>90951</v>
+        <v>91402</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2634,25 +2648,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597436</v>
+        <v>597391</v>
       </c>
       <c r="R21" t="n">
-        <v>7030329</v>
+        <v>7030295</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2724,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123052146</v>
+        <v>123041570</v>
       </c>
       <c r="B22" t="n">
-        <v>57634</v>
+        <v>90957</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,43 +2754,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597309</v>
+        <v>597395</v>
       </c>
       <c r="R22" t="n">
-        <v>7030317</v>
+        <v>7030312</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2835,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123041564</v>
+        <v>123052262</v>
       </c>
       <c r="B23" t="n">
-        <v>91400</v>
+        <v>90957</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2847,25 +2852,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2880,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597391</v>
+        <v>597377</v>
       </c>
       <c r="R23" t="n">
-        <v>7030308</v>
+        <v>7030279</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2937,10 +2942,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123041379</v>
+        <v>123052224</v>
       </c>
       <c r="B24" t="n">
-        <v>91242</v>
+        <v>90953</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2953,21 +2958,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2977,10 +2982,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597386</v>
+        <v>597309</v>
       </c>
       <c r="R24" t="n">
-        <v>7030293</v>
+        <v>7030317</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3039,10 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123043324</v>
+        <v>123044316</v>
       </c>
       <c r="B25" t="n">
-        <v>90955</v>
+        <v>79887</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3051,25 +3056,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +3084,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597342</v>
+        <v>597313</v>
       </c>
       <c r="R25" t="n">
-        <v>7030326</v>
+        <v>7030320</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3141,10 +3146,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123041955</v>
+        <v>123040637</v>
       </c>
       <c r="B26" t="n">
-        <v>90955</v>
+        <v>91355</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3157,21 +3162,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597379</v>
+        <v>597437</v>
       </c>
       <c r="R26" t="n">
-        <v>7030360</v>
+        <v>7030292</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3243,10 +3243,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123040568</v>
+        <v>123041564</v>
       </c>
       <c r="B27" t="n">
-        <v>91400</v>
+        <v>91402</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597441</v>
+        <v>597391</v>
       </c>
       <c r="R27" t="n">
-        <v>7030301</v>
+        <v>7030308</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3348,7 +3348,7 @@
         <v>123044293</v>
       </c>
       <c r="B28" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123044289</v>
+        <v>123045077</v>
       </c>
       <c r="B29" t="n">
-        <v>79879</v>
+        <v>90922</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597317</v>
+        <v>597313</v>
       </c>
       <c r="R29" t="n">
-        <v>7030322</v>
+        <v>7030320</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123052262</v>
+        <v>123041496</v>
       </c>
       <c r="B30" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597377</v>
+        <v>597392</v>
       </c>
       <c r="R30" t="n">
-        <v>7030279</v>
+        <v>7030296</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123041496</v>
+        <v>123039722</v>
       </c>
       <c r="B31" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597392</v>
+        <v>597461</v>
       </c>
       <c r="R31" t="n">
-        <v>7030296</v>
+        <v>7030329</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123049756</v>
+        <v>123044289</v>
       </c>
       <c r="B32" t="n">
-        <v>90951</v>
+        <v>79881</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3765,25 +3765,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597344</v>
+        <v>597317</v>
       </c>
       <c r="R32" t="n">
-        <v>7030297</v>
+        <v>7030322</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123051419</v>
+        <v>123041531</v>
       </c>
       <c r="B33" t="n">
-        <v>90951</v>
+        <v>90953</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597335</v>
+        <v>597390</v>
       </c>
       <c r="R33" t="n">
-        <v>7030341</v>
+        <v>7030296</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3960,7 +3960,7 @@
         <v>123071993</v>
       </c>
       <c r="B34" t="n">
-        <v>91616</v>
+        <v>91618</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123042680</v>
+        <v>123044251</v>
       </c>
       <c r="B3" t="n">
-        <v>91244</v>
+        <v>90957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597383</v>
+        <v>597321</v>
       </c>
       <c r="R3" t="n">
-        <v>7030347</v>
+        <v>7030312</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123044251</v>
+        <v>123042680</v>
       </c>
       <c r="B4" t="n">
-        <v>90957</v>
+        <v>91244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597321</v>
+        <v>597383</v>
       </c>
       <c r="R4" t="n">
-        <v>7030312</v>
+        <v>7030347</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123044251</v>
+        <v>123052146</v>
       </c>
       <c r="B3" t="n">
-        <v>90957</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +807,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597321</v>
+        <v>597309</v>
       </c>
       <c r="R3" t="n">
-        <v>7030312</v>
+        <v>7030317</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -893,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123042680</v>
+        <v>123044316</v>
       </c>
       <c r="B4" t="n">
-        <v>91244</v>
+        <v>79888</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,25 +914,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597383</v>
+        <v>597313</v>
       </c>
       <c r="R4" t="n">
-        <v>7030347</v>
+        <v>7030320</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123041379</v>
+        <v>123052224</v>
       </c>
       <c r="B5" t="n">
-        <v>91244</v>
+        <v>90959</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597386</v>
+        <v>597309</v>
       </c>
       <c r="R5" t="n">
-        <v>7030293</v>
+        <v>7030317</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1097,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123039951</v>
+        <v>123041901</v>
       </c>
       <c r="B6" t="n">
-        <v>90957</v>
+        <v>90959</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1122,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597462</v>
+        <v>597380</v>
       </c>
       <c r="R6" t="n">
-        <v>7030312</v>
+        <v>7030371</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1199,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123040577</v>
+        <v>123043324</v>
       </c>
       <c r="B7" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597442</v>
+        <v>597342</v>
       </c>
       <c r="R7" t="n">
-        <v>7030306</v>
+        <v>7030326</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1301,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123041955</v>
+        <v>123050244</v>
       </c>
       <c r="B8" t="n">
-        <v>90957</v>
+        <v>90959</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597379</v>
+        <v>597436</v>
       </c>
       <c r="R8" t="n">
-        <v>7030360</v>
+        <v>7030329</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1403,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123040568</v>
+        <v>123045077</v>
       </c>
       <c r="B9" t="n">
-        <v>91402</v>
+        <v>90928</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,25 +1424,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597441</v>
+        <v>597313</v>
       </c>
       <c r="R9" t="n">
-        <v>7030301</v>
+        <v>7030320</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123043079</v>
+        <v>123042680</v>
       </c>
       <c r="B10" t="n">
-        <v>90922</v>
+        <v>91250</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,25 +1526,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597393</v>
+        <v>597383</v>
       </c>
       <c r="R10" t="n">
-        <v>7030365</v>
+        <v>7030347</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1607,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123050244</v>
+        <v>123042937</v>
       </c>
       <c r="B11" t="n">
-        <v>90953</v>
+        <v>90963</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,21 +1632,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597436</v>
+        <v>597397</v>
       </c>
       <c r="R11" t="n">
-        <v>7030329</v>
+        <v>7030367</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123042937</v>
+        <v>123041955</v>
       </c>
       <c r="B12" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597397</v>
+        <v>597379</v>
       </c>
       <c r="R12" t="n">
-        <v>7030367</v>
+        <v>7030360</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1811,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123051419</v>
+        <v>123044293</v>
       </c>
       <c r="B13" t="n">
-        <v>90953</v>
+        <v>79853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,21 +1836,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597335</v>
+        <v>597316</v>
       </c>
       <c r="R13" t="n">
-        <v>7030341</v>
+        <v>7030324</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1913,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123044298</v>
+        <v>123039792</v>
       </c>
       <c r="B14" t="n">
-        <v>79852</v>
+        <v>91250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1929,21 +1938,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1953,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597315</v>
+        <v>597458</v>
       </c>
       <c r="R14" t="n">
-        <v>7030325</v>
+        <v>7030292</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2015,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123042345</v>
+        <v>123039722</v>
       </c>
       <c r="B15" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2055,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597413</v>
+        <v>597461</v>
       </c>
       <c r="R15" t="n">
-        <v>7030346</v>
+        <v>7030329</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2117,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123052146</v>
+        <v>123040577</v>
       </c>
       <c r="B16" t="n">
-        <v>57634</v>
+        <v>90963</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,43 +2142,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597309</v>
+        <v>597442</v>
       </c>
       <c r="R16" t="n">
-        <v>7030317</v>
+        <v>7030306</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123043324</v>
+        <v>123049756</v>
       </c>
       <c r="B17" t="n">
-        <v>90957</v>
+        <v>90959</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597342</v>
+        <v>597344</v>
       </c>
       <c r="R17" t="n">
-        <v>7030326</v>
+        <v>7030297</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123049756</v>
+        <v>123044298</v>
       </c>
       <c r="B18" t="n">
-        <v>90953</v>
+        <v>79853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597344</v>
+        <v>597315</v>
       </c>
       <c r="R18" t="n">
-        <v>7030297</v>
+        <v>7030325</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123041901</v>
+        <v>123041379</v>
       </c>
       <c r="B19" t="n">
-        <v>90953</v>
+        <v>91250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2448,21 +2448,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597380</v>
+        <v>597386</v>
       </c>
       <c r="R19" t="n">
-        <v>7030371</v>
+        <v>7030293</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123039792</v>
+        <v>123041564</v>
       </c>
       <c r="B20" t="n">
-        <v>91244</v>
+        <v>91408</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,25 +2546,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597458</v>
+        <v>597391</v>
       </c>
       <c r="R20" t="n">
-        <v>7030292</v>
+        <v>7030308</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123041516</v>
+        <v>123052262</v>
       </c>
       <c r="B21" t="n">
-        <v>91402</v>
+        <v>90963</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2648,25 +2648,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597391</v>
+        <v>597377</v>
       </c>
       <c r="R21" t="n">
-        <v>7030295</v>
+        <v>7030279</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123041570</v>
+        <v>123043079</v>
       </c>
       <c r="B22" t="n">
-        <v>90957</v>
+        <v>90928</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2750,25 +2750,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597395</v>
+        <v>597393</v>
       </c>
       <c r="R22" t="n">
-        <v>7030312</v>
+        <v>7030365</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123052262</v>
+        <v>123041531</v>
       </c>
       <c r="B23" t="n">
-        <v>90957</v>
+        <v>90959</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2856,21 +2856,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597377</v>
+        <v>597390</v>
       </c>
       <c r="R23" t="n">
-        <v>7030279</v>
+        <v>7030296</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123052224</v>
+        <v>123044289</v>
       </c>
       <c r="B24" t="n">
-        <v>90953</v>
+        <v>79882</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2954,25 +2954,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597309</v>
+        <v>597317</v>
       </c>
       <c r="R24" t="n">
-        <v>7030317</v>
+        <v>7030322</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123044316</v>
+        <v>123041516</v>
       </c>
       <c r="B25" t="n">
-        <v>79887</v>
+        <v>91408</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3056,25 +3056,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597313</v>
+        <v>597391</v>
       </c>
       <c r="R25" t="n">
-        <v>7030320</v>
+        <v>7030295</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123040637</v>
+        <v>123041496</v>
       </c>
       <c r="B26" t="n">
-        <v>91355</v>
+        <v>90963</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3162,16 +3162,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597437</v>
+        <v>597392</v>
       </c>
       <c r="R26" t="n">
-        <v>7030292</v>
+        <v>7030296</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3243,10 +3248,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123041564</v>
+        <v>123040568</v>
       </c>
       <c r="B27" t="n">
-        <v>91402</v>
+        <v>91408</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3283,10 +3288,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597391</v>
+        <v>597441</v>
       </c>
       <c r="R27" t="n">
-        <v>7030308</v>
+        <v>7030301</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3345,10 +3350,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123044293</v>
+        <v>123042345</v>
       </c>
       <c r="B28" t="n">
-        <v>79852</v>
+        <v>90963</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3361,21 +3366,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3385,10 +3390,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597316</v>
+        <v>597413</v>
       </c>
       <c r="R28" t="n">
-        <v>7030324</v>
+        <v>7030346</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3447,10 +3452,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123045077</v>
+        <v>123039951</v>
       </c>
       <c r="B29" t="n">
-        <v>90922</v>
+        <v>90963</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3459,25 +3464,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3487,10 +3492,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597313</v>
+        <v>597462</v>
       </c>
       <c r="R29" t="n">
-        <v>7030320</v>
+        <v>7030312</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,10 +3554,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123041496</v>
+        <v>123044251</v>
       </c>
       <c r="B30" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3589,10 +3594,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597392</v>
+        <v>597321</v>
       </c>
       <c r="R30" t="n">
-        <v>7030296</v>
+        <v>7030312</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,10 +3656,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123039722</v>
+        <v>123040637</v>
       </c>
       <c r="B31" t="n">
-        <v>90957</v>
+        <v>91361</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3667,21 +3672,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597461</v>
+        <v>597437</v>
       </c>
       <c r="R31" t="n">
-        <v>7030329</v>
+        <v>7030292</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123044289</v>
+        <v>123051419</v>
       </c>
       <c r="B32" t="n">
-        <v>79881</v>
+        <v>90959</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3765,25 +3765,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597317</v>
+        <v>597335</v>
       </c>
       <c r="R32" t="n">
-        <v>7030322</v>
+        <v>7030341</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3855,10 +3855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123041531</v>
+        <v>123041570</v>
       </c>
       <c r="B33" t="n">
-        <v>90953</v>
+        <v>90963</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3871,21 +3871,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597390</v>
+        <v>597395</v>
       </c>
       <c r="R33" t="n">
-        <v>7030296</v>
+        <v>7030312</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3960,7 +3960,7 @@
         <v>123071993</v>
       </c>
       <c r="B34" t="n">
-        <v>91618</v>
+        <v>91624</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123040577</v>
+        <v>123052146</v>
       </c>
       <c r="B13" t="n">
-        <v>90966</v>
+        <v>57634</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,34 +1827,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597442</v>
+        <v>597309</v>
       </c>
       <c r="R13" t="n">
-        <v>7030306</v>
+        <v>7030317</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1913,7 +1922,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123041570</v>
+        <v>123040577</v>
       </c>
       <c r="B14" t="n">
         <v>90966</v>
@@ -1953,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597395</v>
+        <v>597442</v>
       </c>
       <c r="R14" t="n">
-        <v>7030312</v>
+        <v>7030306</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2015,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123044316</v>
+        <v>123041570</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>90966</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,25 +2036,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597313</v>
+        <v>597395</v>
       </c>
       <c r="R15" t="n">
-        <v>7030320</v>
+        <v>7030312</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2117,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123044289</v>
+        <v>123044316</v>
       </c>
       <c r="B16" t="n">
-        <v>79885</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2133,21 +2142,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597317</v>
+        <v>597313</v>
       </c>
       <c r="R16" t="n">
-        <v>7030322</v>
+        <v>7030320</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2219,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123052146</v>
+        <v>123044289</v>
       </c>
       <c r="B17" t="n">
-        <v>57634</v>
+        <v>79885</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2231,47 +2240,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597309</v>
+        <v>597317</v>
       </c>
       <c r="R17" t="n">
-        <v>7030317</v>
+        <v>7030322</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123052224</v>
+        <v>123041496</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597309</v>
+        <v>597392</v>
       </c>
       <c r="R3" t="n">
-        <v>7030317</v>
+        <v>7030296</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123040568</v>
+        <v>123041570</v>
       </c>
       <c r="B4" t="n">
-        <v>91411</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,25 +905,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597441</v>
+        <v>597395</v>
       </c>
       <c r="R4" t="n">
-        <v>7030301</v>
+        <v>7030312</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123039722</v>
+        <v>123044251</v>
       </c>
       <c r="B5" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597461</v>
+        <v>597321</v>
       </c>
       <c r="R5" t="n">
-        <v>7030329</v>
+        <v>7030312</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123041516</v>
+        <v>123042680</v>
       </c>
       <c r="B6" t="n">
-        <v>91411</v>
+        <v>91270</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,25 +1109,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597391</v>
+        <v>597383</v>
       </c>
       <c r="R6" t="n">
-        <v>7030295</v>
+        <v>7030347</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123043324</v>
+        <v>123039951</v>
       </c>
       <c r="B7" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597342</v>
+        <v>597462</v>
       </c>
       <c r="R7" t="n">
-        <v>7030326</v>
+        <v>7030312</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123041564</v>
+        <v>123041516</v>
       </c>
       <c r="B8" t="n">
-        <v>91411</v>
+        <v>91428</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>597391</v>
       </c>
       <c r="R8" t="n">
-        <v>7030308</v>
+        <v>7030295</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123039792</v>
+        <v>123041564</v>
       </c>
       <c r="B9" t="n">
-        <v>91253</v>
+        <v>91428</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,25 +1415,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597458</v>
+        <v>597391</v>
       </c>
       <c r="R9" t="n">
-        <v>7030292</v>
+        <v>7030308</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123044298</v>
+        <v>123042345</v>
       </c>
       <c r="B10" t="n">
-        <v>79856</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597315</v>
+        <v>597413</v>
       </c>
       <c r="R10" t="n">
-        <v>7030325</v>
+        <v>7030346</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1610,7 +1610,7 @@
         <v>123049756</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>90979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123044293</v>
+        <v>123039792</v>
       </c>
       <c r="B12" t="n">
-        <v>79856</v>
+        <v>91270</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,21 +1725,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597316</v>
+        <v>597458</v>
       </c>
       <c r="R12" t="n">
-        <v>7030324</v>
+        <v>7030292</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1811,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123052146</v>
+        <v>123042937</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
+        <v>90983</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,43 +1827,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597309</v>
+        <v>597397</v>
       </c>
       <c r="R13" t="n">
-        <v>7030317</v>
+        <v>7030367</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1922,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123040577</v>
+        <v>123041379</v>
       </c>
       <c r="B14" t="n">
-        <v>90966</v>
+        <v>91270</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1938,21 +1929,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1962,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597442</v>
+        <v>597386</v>
       </c>
       <c r="R14" t="n">
-        <v>7030306</v>
+        <v>7030293</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2024,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123041570</v>
+        <v>123041901</v>
       </c>
       <c r="B15" t="n">
-        <v>90966</v>
+        <v>90979</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2040,21 +2031,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2064,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597395</v>
+        <v>597380</v>
       </c>
       <c r="R15" t="n">
-        <v>7030312</v>
+        <v>7030371</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2126,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123044316</v>
+        <v>123040568</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>91428</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,25 +2129,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597313</v>
+        <v>597441</v>
       </c>
       <c r="R16" t="n">
-        <v>7030320</v>
+        <v>7030301</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2228,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123044289</v>
+        <v>123052224</v>
       </c>
       <c r="B17" t="n">
-        <v>79885</v>
+        <v>90979</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,25 +2231,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2268,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597317</v>
+        <v>597309</v>
       </c>
       <c r="R17" t="n">
-        <v>7030322</v>
+        <v>7030317</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2330,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123050244</v>
+        <v>123041955</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>90983</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2346,21 +2337,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2370,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597436</v>
+        <v>597379</v>
       </c>
       <c r="R18" t="n">
-        <v>7030329</v>
+        <v>7030360</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2432,10 +2423,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123039951</v>
+        <v>123041531</v>
       </c>
       <c r="B19" t="n">
-        <v>90966</v>
+        <v>90979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2448,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2472,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597462</v>
+        <v>597390</v>
       </c>
       <c r="R19" t="n">
-        <v>7030312</v>
+        <v>7030296</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2534,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123041531</v>
+        <v>123044316</v>
       </c>
       <c r="B20" t="n">
-        <v>90962</v>
+        <v>79897</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2546,25 +2537,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597390</v>
+        <v>597313</v>
       </c>
       <c r="R20" t="n">
-        <v>7030296</v>
+        <v>7030320</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2636,10 +2627,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123041496</v>
+        <v>123050244</v>
       </c>
       <c r="B21" t="n">
-        <v>90966</v>
+        <v>90979</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2652,21 +2643,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2676,10 +2667,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597392</v>
+        <v>597436</v>
       </c>
       <c r="R21" t="n">
-        <v>7030296</v>
+        <v>7030329</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2738,10 +2729,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123051419</v>
+        <v>123045077</v>
       </c>
       <c r="B22" t="n">
-        <v>90962</v>
+        <v>90948</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2750,25 +2741,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2778,10 +2769,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597335</v>
+        <v>597313</v>
       </c>
       <c r="R22" t="n">
-        <v>7030341</v>
+        <v>7030320</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2840,10 +2831,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123041901</v>
+        <v>123044289</v>
       </c>
       <c r="B23" t="n">
-        <v>90962</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2852,25 +2843,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2880,10 +2871,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597380</v>
+        <v>597317</v>
       </c>
       <c r="R23" t="n">
-        <v>7030371</v>
+        <v>7030322</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2942,10 +2933,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123045077</v>
+        <v>123052262</v>
       </c>
       <c r="B24" t="n">
-        <v>90931</v>
+        <v>90983</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2954,25 +2945,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2982,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597313</v>
+        <v>597377</v>
       </c>
       <c r="R24" t="n">
-        <v>7030320</v>
+        <v>7030279</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3044,10 +3035,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123040637</v>
+        <v>123043079</v>
       </c>
       <c r="B25" t="n">
-        <v>91364</v>
+        <v>90948</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3056,20 +3047,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +3075,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597437</v>
+        <v>597393</v>
       </c>
       <c r="R25" t="n">
-        <v>7030292</v>
+        <v>7030365</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3141,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123041955</v>
+        <v>123044293</v>
       </c>
       <c r="B26" t="n">
-        <v>90966</v>
+        <v>79862</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3157,21 +3153,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3177,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597379</v>
+        <v>597316</v>
       </c>
       <c r="R26" t="n">
-        <v>7030360</v>
+        <v>7030324</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3243,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123044251</v>
+        <v>123039722</v>
       </c>
       <c r="B27" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3283,10 +3279,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597321</v>
+        <v>597461</v>
       </c>
       <c r="R27" t="n">
-        <v>7030312</v>
+        <v>7030329</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3345,10 +3341,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123042937</v>
+        <v>123051419</v>
       </c>
       <c r="B28" t="n">
-        <v>90966</v>
+        <v>90979</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3361,21 +3357,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3385,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597397</v>
+        <v>597335</v>
       </c>
       <c r="R28" t="n">
-        <v>7030367</v>
+        <v>7030341</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3447,10 +3443,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123042680</v>
+        <v>123043324</v>
       </c>
       <c r="B29" t="n">
-        <v>91253</v>
+        <v>90983</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3463,21 +3459,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3487,10 +3483,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597383</v>
+        <v>597342</v>
       </c>
       <c r="R29" t="n">
-        <v>7030347</v>
+        <v>7030326</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3549,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123043079</v>
+        <v>123040577</v>
       </c>
       <c r="B30" t="n">
-        <v>90931</v>
+        <v>90983</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,25 +3557,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3589,10 +3585,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597393</v>
+        <v>597442</v>
       </c>
       <c r="R30" t="n">
-        <v>7030365</v>
+        <v>7030306</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3651,10 +3647,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123052262</v>
+        <v>123044298</v>
       </c>
       <c r="B31" t="n">
-        <v>90966</v>
+        <v>79862</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3667,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3691,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597377</v>
+        <v>597315</v>
       </c>
       <c r="R31" t="n">
-        <v>7030279</v>
+        <v>7030325</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3753,10 +3749,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123041379</v>
+        <v>123052146</v>
       </c>
       <c r="B32" t="n">
-        <v>91253</v>
+        <v>57640</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3769,34 +3765,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597386</v>
+        <v>597309</v>
       </c>
       <c r="R32" t="n">
-        <v>7030293</v>
+        <v>7030317</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3855,10 +3860,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123042345</v>
+        <v>123040637</v>
       </c>
       <c r="B33" t="n">
-        <v>90966</v>
+        <v>91381</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3871,21 +3876,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597413</v>
+        <v>597437</v>
       </c>
       <c r="R33" t="n">
-        <v>7030346</v>
+        <v>7030292</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3960,7 +3960,7 @@
         <v>123071993</v>
       </c>
       <c r="B34" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -2219,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123052224</v>
+        <v>123041955</v>
       </c>
       <c r="B17" t="n">
-        <v>90979</v>
+        <v>90983</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597309</v>
+        <v>597379</v>
       </c>
       <c r="R17" t="n">
-        <v>7030317</v>
+        <v>7030360</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123041955</v>
+        <v>123041531</v>
       </c>
       <c r="B18" t="n">
-        <v>90983</v>
+        <v>90979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597379</v>
+        <v>597390</v>
       </c>
       <c r="R18" t="n">
-        <v>7030360</v>
+        <v>7030296</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123041531</v>
+        <v>123052224</v>
       </c>
       <c r="B19" t="n">
         <v>90979</v>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597390</v>
+        <v>597309</v>
       </c>
       <c r="R19" t="n">
-        <v>7030296</v>
+        <v>7030317</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3545,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123040577</v>
+        <v>123044298</v>
       </c>
       <c r="B30" t="n">
-        <v>90983</v>
+        <v>79862</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,21 +3561,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597442</v>
+        <v>597315</v>
       </c>
       <c r="R30" t="n">
-        <v>7030306</v>
+        <v>7030325</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123044298</v>
+        <v>123040577</v>
       </c>
       <c r="B31" t="n">
-        <v>79862</v>
+        <v>90983</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3663,21 +3663,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597315</v>
+        <v>597442</v>
       </c>
       <c r="R31" t="n">
-        <v>7030325</v>
+        <v>7030306</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -2219,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123041955</v>
+        <v>123052224</v>
       </c>
       <c r="B17" t="n">
-        <v>90983</v>
+        <v>90979</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2235,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597379</v>
+        <v>597309</v>
       </c>
       <c r="R17" t="n">
-        <v>7030360</v>
+        <v>7030317</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123041531</v>
+        <v>123041955</v>
       </c>
       <c r="B18" t="n">
-        <v>90979</v>
+        <v>90983</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,21 +2337,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597390</v>
+        <v>597379</v>
       </c>
       <c r="R18" t="n">
-        <v>7030296</v>
+        <v>7030360</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123052224</v>
+        <v>123041531</v>
       </c>
       <c r="B19" t="n">
         <v>90979</v>
@@ -2463,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597309</v>
+        <v>597390</v>
       </c>
       <c r="R19" t="n">
-        <v>7030317</v>
+        <v>7030296</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2831,10 +2831,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123044289</v>
+        <v>123052262</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>90983</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,25 +2843,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597317</v>
+        <v>597377</v>
       </c>
       <c r="R23" t="n">
-        <v>7030322</v>
+        <v>7030279</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123052262</v>
+        <v>123044289</v>
       </c>
       <c r="B24" t="n">
-        <v>90983</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,25 +2945,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597377</v>
+        <v>597317</v>
       </c>
       <c r="R24" t="n">
-        <v>7030279</v>
+        <v>7030322</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -2831,10 +2831,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123052262</v>
+        <v>123044289</v>
       </c>
       <c r="B23" t="n">
-        <v>90983</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,25 +2843,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597377</v>
+        <v>597317</v>
       </c>
       <c r="R23" t="n">
-        <v>7030279</v>
+        <v>7030322</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2933,10 +2933,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123044289</v>
+        <v>123052262</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>90983</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2945,25 +2945,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597317</v>
+        <v>597377</v>
       </c>
       <c r="R24" t="n">
-        <v>7030322</v>
+        <v>7030279</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123044293</v>
+        <v>123039722</v>
       </c>
       <c r="B26" t="n">
-        <v>79862</v>
+        <v>90983</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3153,21 +3153,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597316</v>
+        <v>597461</v>
       </c>
       <c r="R26" t="n">
-        <v>7030324</v>
+        <v>7030329</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3239,10 +3239,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123039722</v>
+        <v>123044293</v>
       </c>
       <c r="B27" t="n">
-        <v>90983</v>
+        <v>79862</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3255,21 +3255,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>597461</v>
+        <v>597316</v>
       </c>
       <c r="R27" t="n">
-        <v>7030329</v>
+        <v>7030324</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123041496</v>
+        <v>123045077</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>90953</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597392</v>
+        <v>597313</v>
       </c>
       <c r="R3" t="n">
-        <v>7030296</v>
+        <v>7030320</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123041570</v>
+        <v>123039951</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597395</v>
+        <v>597462</v>
       </c>
       <c r="R4" t="n">
         <v>7030312</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123044251</v>
+        <v>123041379</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>91275</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597321</v>
+        <v>597386</v>
       </c>
       <c r="R5" t="n">
-        <v>7030312</v>
+        <v>7030293</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123042680</v>
+        <v>123052262</v>
       </c>
       <c r="B6" t="n">
-        <v>91270</v>
+        <v>90988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597383</v>
+        <v>597377</v>
       </c>
       <c r="R6" t="n">
-        <v>7030347</v>
+        <v>7030279</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123039951</v>
+        <v>123052146</v>
       </c>
       <c r="B7" t="n">
-        <v>90983</v>
+        <v>57643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,34 +1215,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597462</v>
+        <v>597309</v>
       </c>
       <c r="R7" t="n">
-        <v>7030312</v>
+        <v>7030317</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1301,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123041516</v>
+        <v>123040577</v>
       </c>
       <c r="B8" t="n">
-        <v>91428</v>
+        <v>90988</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,25 +1322,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597391</v>
+        <v>597442</v>
       </c>
       <c r="R8" t="n">
-        <v>7030295</v>
+        <v>7030306</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1403,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123041564</v>
+        <v>123043324</v>
       </c>
       <c r="B9" t="n">
-        <v>91428</v>
+        <v>90988</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,25 +1424,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597391</v>
+        <v>597342</v>
       </c>
       <c r="R9" t="n">
-        <v>7030308</v>
+        <v>7030326</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1505,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123042345</v>
+        <v>123041516</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>91433</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,25 +1526,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597413</v>
+        <v>597391</v>
       </c>
       <c r="R10" t="n">
-        <v>7030346</v>
+        <v>7030295</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1607,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123049756</v>
+        <v>123050244</v>
       </c>
       <c r="B11" t="n">
-        <v>90979</v>
+        <v>90984</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597344</v>
+        <v>597436</v>
       </c>
       <c r="R11" t="n">
-        <v>7030297</v>
+        <v>7030329</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1709,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123039792</v>
+        <v>123042680</v>
       </c>
       <c r="B12" t="n">
-        <v>91270</v>
+        <v>91275</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597458</v>
+        <v>597383</v>
       </c>
       <c r="R12" t="n">
-        <v>7030292</v>
+        <v>7030347</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1811,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123042937</v>
+        <v>123043079</v>
       </c>
       <c r="B13" t="n">
-        <v>90983</v>
+        <v>90953</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,25 +1832,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597397</v>
+        <v>597393</v>
       </c>
       <c r="R13" t="n">
-        <v>7030367</v>
+        <v>7030365</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1913,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123041379</v>
+        <v>123044289</v>
       </c>
       <c r="B14" t="n">
-        <v>91270</v>
+        <v>79896</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,25 +1934,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1953,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597386</v>
+        <v>597317</v>
       </c>
       <c r="R14" t="n">
-        <v>7030293</v>
+        <v>7030322</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2015,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123041901</v>
+        <v>123041564</v>
       </c>
       <c r="B15" t="n">
-        <v>90979</v>
+        <v>91433</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,25 +2036,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597380</v>
+        <v>597391</v>
       </c>
       <c r="R15" t="n">
-        <v>7030371</v>
+        <v>7030308</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2117,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123040568</v>
+        <v>123044316</v>
       </c>
       <c r="B16" t="n">
-        <v>91428</v>
+        <v>79902</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,25 +2138,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2157,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597441</v>
+        <v>597313</v>
       </c>
       <c r="R16" t="n">
-        <v>7030301</v>
+        <v>7030320</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2219,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123052224</v>
+        <v>123044298</v>
       </c>
       <c r="B17" t="n">
-        <v>90979</v>
+        <v>79867</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2235,21 +2244,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2259,10 +2268,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597309</v>
+        <v>597315</v>
       </c>
       <c r="R17" t="n">
-        <v>7030317</v>
+        <v>7030325</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2321,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123041955</v>
+        <v>123042345</v>
       </c>
       <c r="B18" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2361,10 +2370,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597379</v>
+        <v>597413</v>
       </c>
       <c r="R18" t="n">
-        <v>7030360</v>
+        <v>7030346</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2423,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123041531</v>
+        <v>123041570</v>
       </c>
       <c r="B19" t="n">
-        <v>90979</v>
+        <v>90988</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2439,21 +2448,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2463,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597390</v>
+        <v>597395</v>
       </c>
       <c r="R19" t="n">
-        <v>7030296</v>
+        <v>7030312</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2525,10 +2534,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123044316</v>
+        <v>123052224</v>
       </c>
       <c r="B20" t="n">
-        <v>79897</v>
+        <v>90984</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2537,25 +2546,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2565,10 +2574,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597313</v>
+        <v>597309</v>
       </c>
       <c r="R20" t="n">
-        <v>7030320</v>
+        <v>7030317</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2627,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123050244</v>
+        <v>123041531</v>
       </c>
       <c r="B21" t="n">
-        <v>90979</v>
+        <v>90984</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2667,10 +2676,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>597436</v>
+        <v>597390</v>
       </c>
       <c r="R21" t="n">
-        <v>7030329</v>
+        <v>7030296</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2729,10 +2738,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123045077</v>
+        <v>123042937</v>
       </c>
       <c r="B22" t="n">
-        <v>90948</v>
+        <v>90988</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,25 +2750,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2769,10 +2778,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597313</v>
+        <v>597397</v>
       </c>
       <c r="R22" t="n">
-        <v>7030320</v>
+        <v>7030367</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2831,10 +2840,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123044289</v>
+        <v>123041955</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>90988</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,25 +2852,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2871,10 +2880,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597317</v>
+        <v>597379</v>
       </c>
       <c r="R23" t="n">
-        <v>7030322</v>
+        <v>7030360</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2933,10 +2942,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123052262</v>
+        <v>123051419</v>
       </c>
       <c r="B24" t="n">
-        <v>90983</v>
+        <v>90984</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2949,21 +2958,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2973,10 +2982,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597377</v>
+        <v>597335</v>
       </c>
       <c r="R24" t="n">
-        <v>7030279</v>
+        <v>7030341</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3035,10 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123043079</v>
+        <v>123039792</v>
       </c>
       <c r="B25" t="n">
-        <v>90948</v>
+        <v>91275</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3047,25 +3056,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3075,10 +3084,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>597393</v>
+        <v>597458</v>
       </c>
       <c r="R25" t="n">
-        <v>7030365</v>
+        <v>7030292</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3137,10 +3146,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123039722</v>
+        <v>123041901</v>
       </c>
       <c r="B26" t="n">
-        <v>90983</v>
+        <v>90984</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3153,21 +3162,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3177,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597461</v>
+        <v>597380</v>
       </c>
       <c r="R26" t="n">
-        <v>7030329</v>
+        <v>7030371</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3242,7 +3251,7 @@
         <v>123044293</v>
       </c>
       <c r="B27" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3341,10 +3350,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123051419</v>
+        <v>123040637</v>
       </c>
       <c r="B28" t="n">
-        <v>90979</v>
+        <v>91386</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3357,21 +3366,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3385,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597335</v>
+        <v>597437</v>
       </c>
       <c r="R28" t="n">
-        <v>7030341</v>
+        <v>7030292</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3443,10 +3447,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123043324</v>
+        <v>123039722</v>
       </c>
       <c r="B29" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3483,10 +3487,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597342</v>
+        <v>597461</v>
       </c>
       <c r="R29" t="n">
-        <v>7030326</v>
+        <v>7030329</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3545,10 +3549,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123044298</v>
+        <v>123041496</v>
       </c>
       <c r="B30" t="n">
-        <v>79862</v>
+        <v>90988</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,21 +3565,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3585,10 +3589,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>597315</v>
+        <v>597392</v>
       </c>
       <c r="R30" t="n">
-        <v>7030325</v>
+        <v>7030296</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3647,10 +3651,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123040577</v>
+        <v>123044251</v>
       </c>
       <c r="B31" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3687,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>597442</v>
+        <v>597321</v>
       </c>
       <c r="R31" t="n">
-        <v>7030306</v>
+        <v>7030312</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3749,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123052146</v>
+        <v>123049756</v>
       </c>
       <c r="B32" t="n">
-        <v>57640</v>
+        <v>90984</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3765,43 +3769,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sörtannflo, Sörtannflo, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>597309</v>
+        <v>597344</v>
       </c>
       <c r="R32" t="n">
-        <v>7030317</v>
+        <v>7030297</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3860,10 +3855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123040637</v>
+        <v>123040568</v>
       </c>
       <c r="B33" t="n">
-        <v>91381</v>
+        <v>91433</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3872,20 +3867,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>597437</v>
+        <v>597441</v>
       </c>
       <c r="R33" t="n">
-        <v>7030292</v>
+        <v>7030301</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3960,7 +3960,7 @@
         <v>123071993</v>
       </c>
       <c r="B34" t="n">
-        <v>91644</v>
+        <v>91649</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -3960,7 +3960,7 @@
         <v>123071993</v>
       </c>
       <c r="B34" t="n">
-        <v>91649</v>
+        <v>91651</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4061,6 +4061,394 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126270216</v>
+      </c>
+      <c r="B35" t="n">
+        <v>100434</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>597453</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7030279</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126269100</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91534</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>658</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>597400</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7030292</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126269892</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91534</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>658</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>597362</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7030273</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126268990</v>
+      </c>
+      <c r="B38" t="n">
+        <v>100434</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sörtannflo, Sörtannflo, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>597448</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7030308</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -4066,7 +4066,7 @@
         <v>126270216</v>
       </c>
       <c r="B35" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>126269100</v>
       </c>
       <c r="B36" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>126269892</v>
       </c>
       <c r="B37" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>126268990</v>
       </c>
       <c r="B38" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -4066,7 +4066,7 @@
         <v>126270216</v>
       </c>
       <c r="B35" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>126268990</v>
       </c>
       <c r="B38" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 3325-2025 artfynd.xlsx
+++ b/artfynd/A 3325-2025 artfynd.xlsx
@@ -4066,7 +4066,7 @@
         <v>126270216</v>
       </c>
       <c r="B35" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>126269100</v>
       </c>
       <c r="B36" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>126269892</v>
       </c>
       <c r="B37" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>126268990</v>
       </c>
       <c r="B38" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
